--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
@@ -5640,7 +5640,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
@@ -5640,7 +5640,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
@@ -5640,7 +5640,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
@@ -5640,7 +5640,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
@@ -5640,7 +5640,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
@@ -5640,7 +5640,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260327_202848.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
